--- a/diseases/d208/2020-2025.xlsx
+++ b/diseases/d208/2020-2025.xlsx
@@ -14877,14 +14877,12 @@
       <c r="O100" t="n">
         <v>172</v>
       </c>
+      <c r="P100" t="n">
+        <v>172</v>
+      </c>
       <c r="R100" t="n">
         <v>0.04979350589680027</v>
       </c>
-      <c r="S100" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -14897,23 +14895,13 @@
       </c>
       <c r="AP100" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR100" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS100" t="inlineStr"/>
       <c r="AT100" t="n">
         <v>0</v>
       </c>
-      <c r="AU100" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV100" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -15027,14 +15015,12 @@
       <c r="O101" t="n">
         <v>50</v>
       </c>
+      <c r="P101" t="n">
+        <v>50</v>
+      </c>
       <c r="R101" t="n">
         <v>0.01447485636534892</v>
       </c>
-      <c r="S101" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -15047,23 +15033,13 @@
       </c>
       <c r="AP101" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR101" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS101" t="inlineStr"/>
       <c r="AT101" t="n">
         <v>0</v>
       </c>
-      <c r="AU101" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV101" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -15177,14 +15153,12 @@
       <c r="O102" t="n">
         <v>149</v>
       </c>
+      <c r="P102" t="n">
+        <v>149</v>
+      </c>
       <c r="R102" t="n">
         <v>0.04313507196873977</v>
       </c>
-      <c r="S102" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -15197,23 +15171,13 @@
       </c>
       <c r="AP102" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR102" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS102" t="inlineStr"/>
       <c r="AT102" t="n">
         <v>0</v>
       </c>
-      <c r="AU102" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV102" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -15327,14 +15291,12 @@
       <c r="O103" t="n">
         <v>74</v>
       </c>
+      <c r="P103" t="n">
+        <v>74</v>
+      </c>
       <c r="R103" t="n">
         <v>0.0214227874207164</v>
       </c>
-      <c r="S103" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -15347,23 +15309,13 @@
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR103" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS103" t="inlineStr"/>
       <c r="AT103" t="n">
         <v>0</v>
       </c>
-      <c r="AU103" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV103" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -15765,14 +15717,12 @@
       <c r="O106" t="n">
         <v>44</v>
       </c>
+      <c r="P106" t="n">
+        <v>44</v>
+      </c>
       <c r="R106" t="n">
         <v>0.01273787360150705</v>
       </c>
-      <c r="S106" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -15785,23 +15735,13 @@
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR106" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS106" t="inlineStr"/>
       <c r="AT106" t="n">
         <v>0</v>
       </c>
-      <c r="AU106" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV106" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -15915,14 +15855,12 @@
       <c r="O107" t="n">
         <v>62</v>
       </c>
+      <c r="P107" t="n">
+        <v>62</v>
+      </c>
       <c r="R107" t="n">
         <v>0.01794882189303266</v>
       </c>
-      <c r="S107" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -15935,23 +15873,13 @@
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR107" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS107" t="inlineStr"/>
       <c r="AT107" t="n">
         <v>0</v>
       </c>
-      <c r="AU107" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV107" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -16065,14 +15993,12 @@
       <c r="O108" t="n">
         <v>55</v>
       </c>
+      <c r="P108" t="n">
+        <v>55</v>
+      </c>
       <c r="R108" t="n">
         <v>0.01592234200188381</v>
       </c>
-      <c r="S108" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -16085,23 +16011,13 @@
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR108" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS108" t="inlineStr"/>
       <c r="AT108" t="n">
         <v>0</v>
       </c>
-      <c r="AU108" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV108" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -16215,14 +16131,12 @@
       <c r="O109" t="n">
         <v>93</v>
       </c>
+      <c r="P109" t="n">
+        <v>93</v>
+      </c>
       <c r="R109" t="n">
         <v>0.02692323283954898</v>
       </c>
-      <c r="S109" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -16235,23 +16149,13 @@
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR109" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS109" t="inlineStr"/>
       <c r="AT109" t="n">
         <v>0</v>
       </c>
-      <c r="AU109" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV109" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -16653,14 +16557,12 @@
       <c r="O112" t="n">
         <v>275</v>
       </c>
+      <c r="P112" t="n">
+        <v>275</v>
+      </c>
       <c r="R112" t="n">
         <v>0.07961171000941905</v>
       </c>
-      <c r="S112" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -16673,23 +16575,13 @@
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR112" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS112" t="inlineStr"/>
       <c r="AT112" t="n">
         <v>0</v>
       </c>
-      <c r="AU112" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV112" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -16803,14 +16695,12 @@
       <c r="O113" t="n">
         <v>112</v>
       </c>
+      <c r="P113" t="n">
+        <v>112</v>
+      </c>
       <c r="R113" t="n">
         <v>0.03242367825838158</v>
       </c>
-      <c r="S113" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -16823,23 +16713,13 @@
       </c>
       <c r="AP113" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR113" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS113" t="inlineStr"/>
       <c r="AT113" t="n">
         <v>0</v>
       </c>
-      <c r="AU113" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV113" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -16953,14 +16833,12 @@
       <c r="O114" t="n">
         <v>317</v>
       </c>
+      <c r="P114" t="n">
+        <v>317</v>
+      </c>
       <c r="R114" t="n">
         <v>0.09177058935631213</v>
       </c>
-      <c r="S114" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -16973,23 +16851,13 @@
       </c>
       <c r="AP114" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR114" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS114" t="inlineStr"/>
       <c r="AT114" t="n">
         <v>0</v>
       </c>
-      <c r="AU114" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV114" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -17103,14 +16971,12 @@
       <c r="O115" t="n">
         <v>125</v>
       </c>
+      <c r="P115" t="n">
+        <v>125</v>
+      </c>
       <c r="R115" t="n">
         <v>0.03618714091337229</v>
       </c>
-      <c r="S115" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -17123,23 +16989,13 @@
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR115" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS115" t="inlineStr"/>
       <c r="AT115" t="n">
         <v>0</v>
       </c>
-      <c r="AU115" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV115" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -17253,14 +17109,12 @@
       <c r="O116" t="n">
         <v>132</v>
       </c>
+      <c r="P116" t="n">
+        <v>132</v>
+      </c>
       <c r="R116" t="n">
         <v>0.03821362080452115</v>
       </c>
-      <c r="S116" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -17273,23 +17127,13 @@
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR116" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS116" t="inlineStr"/>
       <c r="AT116" t="n">
         <v>0</v>
       </c>
-      <c r="AU116" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV116" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -17691,14 +17535,12 @@
       <c r="O119" t="n">
         <v>294</v>
       </c>
+      <c r="P119" t="n">
+        <v>294</v>
+      </c>
       <c r="R119" t="n">
         <v>0.08511215542825164</v>
       </c>
-      <c r="S119" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -17711,23 +17553,13 @@
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR119" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS119" t="inlineStr"/>
       <c r="AT119" t="n">
         <v>0</v>
       </c>
-      <c r="AU119" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV119" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -17841,14 +17673,12 @@
       <c r="O120" t="n">
         <v>141</v>
       </c>
+      <c r="P120" t="n">
+        <v>141</v>
+      </c>
       <c r="R120" t="n">
         <v>0.04081909495028395</v>
       </c>
-      <c r="S120" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -17861,23 +17691,13 @@
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR120" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS120" t="inlineStr"/>
       <c r="AT120" t="n">
         <v>0</v>
       </c>
-      <c r="AU120" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV120" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -17991,14 +17811,12 @@
       <c r="O121" t="n">
         <v>261</v>
       </c>
+      <c r="P121" t="n">
+        <v>261</v>
+      </c>
       <c r="R121" t="n">
         <v>0.07555875022712134</v>
       </c>
-      <c r="S121" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -18011,23 +17829,13 @@
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR121" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS121" t="inlineStr"/>
       <c r="AT121" t="n">
         <v>0</v>
       </c>
-      <c r="AU121" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV121" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -18141,14 +17949,12 @@
       <c r="O122" t="n">
         <v>102</v>
       </c>
+      <c r="P122" t="n">
+        <v>102</v>
+      </c>
       <c r="R122" t="n">
         <v>0.02952870698531179</v>
       </c>
-      <c r="S122" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -18161,23 +17967,13 @@
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR122" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS122" t="inlineStr"/>
       <c r="AT122" t="n">
         <v>0</v>
       </c>
-      <c r="AU122" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV122" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -18579,14 +18375,12 @@
       <c r="O125" t="n">
         <v>252</v>
       </c>
+      <c r="P125" t="n">
+        <v>252</v>
+      </c>
       <c r="R125" t="n">
         <v>0.07295327608135856</v>
       </c>
-      <c r="S125" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -18599,23 +18393,13 @@
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR125" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS125" t="inlineStr"/>
       <c r="AT125" t="n">
         <v>0</v>
       </c>
-      <c r="AU125" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV125" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -18729,14 +18513,12 @@
       <c r="O126" t="n">
         <v>115</v>
       </c>
+      <c r="P126" t="n">
+        <v>115</v>
+      </c>
       <c r="R126" t="n">
         <v>0.03329216964030251</v>
       </c>
-      <c r="S126" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -18749,23 +18531,13 @@
       </c>
       <c r="AP126" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR126" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS126" t="inlineStr"/>
       <c r="AT126" t="n">
         <v>0</v>
       </c>
-      <c r="AU126" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV126" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -18879,14 +18651,12 @@
       <c r="O127" t="n">
         <v>306</v>
       </c>
+      <c r="P127" t="n">
+        <v>306</v>
+      </c>
       <c r="R127" t="n">
         <v>0.08858612095593538</v>
       </c>
-      <c r="S127" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -18899,23 +18669,13 @@
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR127" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS127" t="inlineStr"/>
       <c r="AT127" t="n">
         <v>0</v>
       </c>
-      <c r="AU127" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV127" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -19029,14 +18789,12 @@
       <c r="O128" t="n">
         <v>89</v>
       </c>
+      <c r="P128" t="n">
+        <v>89</v>
+      </c>
       <c r="R128" t="n">
         <v>0.02576524433032108</v>
       </c>
-      <c r="S128" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -19049,23 +18807,13 @@
       </c>
       <c r="AP128" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR128" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS128" t="inlineStr"/>
       <c r="AT128" t="n">
         <v>0</v>
       </c>
-      <c r="AU128" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV128" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -19467,14 +19215,12 @@
       <c r="O131" t="n">
         <v>276</v>
       </c>
+      <c r="P131" t="n">
+        <v>276</v>
+      </c>
       <c r="R131" t="n">
         <v>0.07990120713672604</v>
       </c>
-      <c r="S131" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -19487,23 +19233,13 @@
       </c>
       <c r="AP131" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR131" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS131" t="inlineStr"/>
       <c r="AT131" t="n">
         <v>0</v>
       </c>
-      <c r="AU131" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV131" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -19617,14 +19353,12 @@
       <c r="O132" t="n">
         <v>72</v>
       </c>
+      <c r="P132" t="n">
+        <v>72</v>
+      </c>
       <c r="R132" t="n">
         <v>0.02084379316610244</v>
       </c>
-      <c r="S132" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -19637,23 +19371,13 @@
       </c>
       <c r="AP132" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR132" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS132" t="inlineStr"/>
       <c r="AT132" t="n">
         <v>0</v>
       </c>
-      <c r="AU132" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV132" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -19767,14 +19491,12 @@
       <c r="O133" t="n">
         <v>115</v>
       </c>
+      <c r="P133" t="n">
+        <v>115</v>
+      </c>
       <c r="R133" t="n">
         <v>0.03329216964030251</v>
       </c>
-      <c r="S133" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA133" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -19787,23 +19509,13 @@
       </c>
       <c r="AP133" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR133" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS133" t="inlineStr"/>
       <c r="AT133" t="n">
         <v>0</v>
       </c>
-      <c r="AU133" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV133" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -19917,14 +19629,12 @@
       <c r="O134" t="n">
         <v>242</v>
       </c>
+      <c r="P134" t="n">
+        <v>242</v>
+      </c>
       <c r="R134" t="n">
         <v>0.07005830480828876</v>
       </c>
-      <c r="S134" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -19937,23 +19647,13 @@
       </c>
       <c r="AP134" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR134" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS134" t="inlineStr"/>
       <c r="AT134" t="n">
         <v>0</v>
       </c>
-      <c r="AU134" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV134" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -20067,14 +19767,12 @@
       <c r="O135" t="n">
         <v>93</v>
       </c>
+      <c r="P135" t="n">
+        <v>93</v>
+      </c>
       <c r="R135" t="n">
         <v>0.02692323283954898</v>
       </c>
-      <c r="S135" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -20087,23 +19785,13 @@
       </c>
       <c r="AP135" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR135" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS135" t="inlineStr"/>
       <c r="AT135" t="n">
         <v>0</v>
       </c>
-      <c r="AU135" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV135" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -20505,14 +20193,12 @@
       <c r="O138" t="n">
         <v>253</v>
       </c>
+      <c r="P138" t="n">
+        <v>253</v>
+      </c>
       <c r="R138" t="n">
         <v>0.07324277320866553</v>
       </c>
-      <c r="S138" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA138" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -20525,23 +20211,13 @@
       </c>
       <c r="AP138" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR138" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS138" t="inlineStr"/>
       <c r="AT138" t="n">
         <v>0</v>
       </c>
-      <c r="AU138" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV138" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -20655,14 +20331,12 @@
       <c r="O139" t="n">
         <v>121</v>
       </c>
+      <c r="P139" t="n">
+        <v>121</v>
+      </c>
       <c r="R139" t="n">
         <v>0.03502915240414438</v>
       </c>
-      <c r="S139" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -20675,23 +20349,13 @@
       </c>
       <c r="AP139" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR139" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS139" t="inlineStr"/>
       <c r="AT139" t="n">
         <v>0</v>
       </c>
-      <c r="AU139" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV139" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -20805,14 +20469,12 @@
       <c r="O140" t="n">
         <v>202</v>
       </c>
+      <c r="P140" t="n">
+        <v>202</v>
+      </c>
       <c r="R140" t="n">
         <v>0.05847841971600963</v>
       </c>
-      <c r="S140" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -20825,23 +20487,13 @@
       </c>
       <c r="AP140" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR140" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS140" t="inlineStr"/>
       <c r="AT140" t="n">
         <v>0</v>
       </c>
-      <c r="AU140" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV140" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -20955,14 +20607,12 @@
       <c r="O141" t="n">
         <v>108</v>
       </c>
+      <c r="P141" t="n">
+        <v>108</v>
+      </c>
       <c r="R141" t="n">
         <v>0.03126568974915366</v>
       </c>
-      <c r="S141" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA141" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -20975,23 +20625,13 @@
       </c>
       <c r="AP141" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR141" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS141" t="inlineStr"/>
       <c r="AT141" t="n">
         <v>0</v>
       </c>
-      <c r="AU141" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV141" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -21393,14 +21033,12 @@
       <c r="O144" t="n">
         <v>294</v>
       </c>
+      <c r="P144" t="n">
+        <v>294</v>
+      </c>
       <c r="R144" t="n">
         <v>0.08511215542825164</v>
       </c>
-      <c r="S144" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA144" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -21413,23 +21051,13 @@
       </c>
       <c r="AP144" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR144" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS144" t="inlineStr"/>
       <c r="AT144" t="n">
         <v>0</v>
       </c>
-      <c r="AU144" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV144" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -21543,14 +21171,12 @@
       <c r="O145" t="n">
         <v>100</v>
       </c>
+      <c r="P145" t="n">
+        <v>100</v>
+      </c>
       <c r="R145" t="n">
         <v>0.02894971273069783</v>
       </c>
-      <c r="S145" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA145" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -21563,23 +21189,13 @@
       </c>
       <c r="AP145" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR145" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS145" t="inlineStr"/>
       <c r="AT145" t="n">
         <v>0</v>
       </c>
-      <c r="AU145" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV145" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -21693,14 +21309,12 @@
       <c r="O146" t="n">
         <v>280</v>
       </c>
+      <c r="P146" t="n">
+        <v>280</v>
+      </c>
       <c r="R146" t="n">
         <v>0.08105919564595393</v>
       </c>
-      <c r="S146" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA146" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -21713,23 +21327,13 @@
       </c>
       <c r="AP146" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR146" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS146" t="inlineStr"/>
       <c r="AT146" t="n">
         <v>0</v>
       </c>
-      <c r="AU146" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV146" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -21843,14 +21447,12 @@
       <c r="O147" t="n">
         <v>107</v>
       </c>
+      <c r="P147" t="n">
+        <v>107</v>
+      </c>
       <c r="R147" t="n">
         <v>0.03097619262184668</v>
       </c>
-      <c r="S147" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA147" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -21863,23 +21465,13 @@
       </c>
       <c r="AP147" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR147" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS147" t="inlineStr"/>
       <c r="AT147" t="n">
         <v>0</v>
       </c>
-      <c r="AU147" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV147" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -21993,14 +21585,12 @@
       <c r="O148" t="n">
         <v>111</v>
       </c>
+      <c r="P148" t="n">
+        <v>111</v>
+      </c>
       <c r="R148" t="n">
         <v>0.0321341811310746</v>
       </c>
-      <c r="S148" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -22013,23 +21603,13 @@
       </c>
       <c r="AP148" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR148" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS148" t="inlineStr"/>
       <c r="AT148" t="n">
         <v>0</v>
       </c>
-      <c r="AU148" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV148" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -22431,14 +22011,12 @@
       <c r="O151" t="n">
         <v>318</v>
       </c>
+      <c r="P151" t="n">
+        <v>318</v>
+      </c>
       <c r="R151" t="n">
         <v>0.09206008648361912</v>
       </c>
-      <c r="S151" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA151" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -22451,23 +22029,13 @@
       </c>
       <c r="AP151" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR151" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS151" t="inlineStr"/>
       <c r="AT151" t="n">
         <v>0</v>
       </c>
-      <c r="AU151" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV151" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -22581,14 +22149,12 @@
       <c r="O152" t="n">
         <v>114</v>
       </c>
+      <c r="P152" t="n">
+        <v>114</v>
+      </c>
       <c r="R152" t="n">
         <v>0.03300267251299553</v>
       </c>
-      <c r="S152" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA152" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -22601,23 +22167,13 @@
       </c>
       <c r="AP152" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR152" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS152" t="inlineStr"/>
       <c r="AT152" t="n">
         <v>0</v>
       </c>
-      <c r="AU152" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV152" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -22731,14 +22287,12 @@
       <c r="O153" t="n">
         <v>248</v>
       </c>
+      <c r="P153" t="n">
+        <v>248</v>
+      </c>
       <c r="R153" t="n">
         <v>0.07179528757213063</v>
       </c>
-      <c r="S153" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA153" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -22751,23 +22305,13 @@
       </c>
       <c r="AP153" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR153" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS153" t="inlineStr"/>
       <c r="AT153" t="n">
         <v>0</v>
       </c>
-      <c r="AU153" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV153" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -22881,14 +22425,12 @@
       <c r="O154" t="n">
         <v>124</v>
       </c>
+      <c r="P154" t="n">
+        <v>124</v>
+      </c>
       <c r="R154" t="n">
         <v>0.03589764378606532</v>
       </c>
-      <c r="S154" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA154" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -22901,23 +22443,13 @@
       </c>
       <c r="AP154" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR154" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS154" t="inlineStr"/>
       <c r="AT154" t="n">
         <v>0</v>
       </c>
-      <c r="AU154" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV154" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -23319,14 +22851,12 @@
       <c r="O157" t="n">
         <v>334</v>
       </c>
+      <c r="P157" t="n">
+        <v>334</v>
+      </c>
       <c r="R157" t="n">
         <v>0.09669204052053076</v>
       </c>
-      <c r="S157" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -23339,23 +22869,13 @@
       </c>
       <c r="AP157" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR157" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS157" t="inlineStr"/>
       <c r="AT157" t="n">
         <v>0</v>
       </c>
-      <c r="AU157" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV157" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -23469,14 +22989,12 @@
       <c r="O158" t="n">
         <v>102</v>
       </c>
+      <c r="P158" t="n">
+        <v>102</v>
+      </c>
       <c r="R158" t="n">
         <v>0.02952870698531179</v>
       </c>
-      <c r="S158" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA158" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -23489,23 +23007,13 @@
       </c>
       <c r="AP158" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR158" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS158" t="inlineStr"/>
       <c r="AT158" t="n">
         <v>0</v>
       </c>
-      <c r="AU158" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV158" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -23619,14 +23127,12 @@
       <c r="O159" t="n">
         <v>314</v>
       </c>
+      <c r="P159" t="n">
+        <v>314</v>
+      </c>
       <c r="R159" t="n">
         <v>0.09090209797439121</v>
       </c>
-      <c r="S159" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA159" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -23639,23 +23145,13 @@
       </c>
       <c r="AP159" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR159" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS159" t="inlineStr"/>
       <c r="AT159" t="n">
         <v>0</v>
       </c>
-      <c r="AU159" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV159" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -23769,14 +23265,12 @@
       <c r="O160" t="n">
         <v>135</v>
       </c>
+      <c r="P160" t="n">
+        <v>135</v>
+      </c>
       <c r="R160" t="n">
         <v>0.03908211218644208</v>
       </c>
-      <c r="S160" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA160" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -23789,23 +23283,13 @@
       </c>
       <c r="AP160" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR160" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS160" t="inlineStr"/>
       <c r="AT160" t="n">
         <v>0</v>
       </c>
-      <c r="AU160" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV160" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -24207,14 +23691,12 @@
       <c r="O163" t="n">
         <v>238</v>
       </c>
+      <c r="P163" t="n">
+        <v>238</v>
+      </c>
       <c r="R163" t="n">
         <v>0.06890031629906085</v>
       </c>
-      <c r="S163" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA163" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -24227,23 +23709,13 @@
       </c>
       <c r="AP163" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR163" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS163" t="inlineStr"/>
       <c r="AT163" t="n">
         <v>0</v>
       </c>
-      <c r="AU163" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV163" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -24357,14 +23829,12 @@
       <c r="O164" t="n">
         <v>82</v>
       </c>
+      <c r="P164" t="n">
+        <v>82</v>
+      </c>
       <c r="R164" t="n">
         <v>0.02373876443917223</v>
       </c>
-      <c r="S164" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA164" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -24377,23 +23847,13 @@
       </c>
       <c r="AP164" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR164" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS164" t="inlineStr"/>
       <c r="AT164" t="n">
         <v>0</v>
       </c>
-      <c r="AU164" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV164" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -24507,14 +23967,12 @@
       <c r="O165" t="n">
         <v>308</v>
       </c>
+      <c r="P165" t="n">
+        <v>308</v>
+      </c>
       <c r="R165" t="n">
         <v>0.08916511521054933</v>
       </c>
-      <c r="S165" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA165" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -24527,23 +23985,13 @@
       </c>
       <c r="AP165" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR165" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS165" t="inlineStr"/>
       <c r="AT165" t="n">
         <v>0</v>
       </c>
-      <c r="AU165" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV165" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -24657,14 +24105,12 @@
       <c r="O166" t="n">
         <v>121</v>
       </c>
+      <c r="P166" t="n">
+        <v>121</v>
+      </c>
       <c r="R166" t="n">
         <v>0.03502915240414438</v>
       </c>
-      <c r="S166" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA166" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -24677,23 +24123,13 @@
       </c>
       <c r="AP166" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR166" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS166" t="inlineStr"/>
       <c r="AT166" t="n">
         <v>0</v>
       </c>
-      <c r="AU166" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV166" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -24807,14 +24243,12 @@
       <c r="O167" t="n">
         <v>100</v>
       </c>
+      <c r="P167" t="n">
+        <v>100</v>
+      </c>
       <c r="R167" t="n">
         <v>0.02894971273069783</v>
       </c>
-      <c r="S167" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA167" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -24827,23 +24261,13 @@
       </c>
       <c r="AP167" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR167" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS167" t="inlineStr"/>
       <c r="AT167" t="n">
         <v>0</v>
       </c>
-      <c r="AU167" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV167" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -25245,14 +24669,12 @@
       <c r="O170" t="n">
         <v>330</v>
       </c>
+      <c r="P170" t="n">
+        <v>330</v>
+      </c>
       <c r="R170" t="n">
         <v>0.09553405201130286</v>
       </c>
-      <c r="S170" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA170" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -25265,23 +24687,13 @@
       </c>
       <c r="AP170" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR170" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS170" t="inlineStr"/>
       <c r="AT170" t="n">
         <v>0</v>
       </c>
-      <c r="AU170" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV170" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -25395,14 +24807,12 @@
       <c r="O171" t="n">
         <v>144</v>
       </c>
+      <c r="P171" t="n">
+        <v>144</v>
+      </c>
       <c r="R171" t="n">
         <v>0.04168758633220489</v>
       </c>
-      <c r="S171" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA171" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -25415,23 +24825,13 @@
       </c>
       <c r="AP171" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR171" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS171" t="inlineStr"/>
       <c r="AT171" t="n">
         <v>0</v>
       </c>
-      <c r="AU171" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV171" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -25545,14 +24945,12 @@
       <c r="O172" t="n">
         <v>263</v>
       </c>
+      <c r="P172" t="n">
+        <v>263</v>
+      </c>
       <c r="R172" t="n">
         <v>0.07613774448173531</v>
       </c>
-      <c r="S172" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA172" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -25565,23 +24963,13 @@
       </c>
       <c r="AP172" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR172" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS172" t="inlineStr"/>
       <c r="AT172" t="n">
         <v>0</v>
       </c>
-      <c r="AU172" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV172" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -25695,14 +25083,12 @@
       <c r="O173" t="n">
         <v>53</v>
       </c>
+      <c r="P173" t="n">
+        <v>53</v>
+      </c>
       <c r="R173" t="n">
         <v>0.01534334774726985</v>
       </c>
-      <c r="S173" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA173" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -25715,23 +25101,13 @@
       </c>
       <c r="AP173" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR173" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS173" t="inlineStr"/>
       <c r="AT173" t="n">
         <v>0</v>
       </c>
-      <c r="AU173" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV173" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -26133,14 +25509,12 @@
       <c r="O176" t="n">
         <v>263</v>
       </c>
+      <c r="P176" t="n">
+        <v>263</v>
+      </c>
       <c r="R176" t="n">
         <v>0.07573231256542395</v>
       </c>
-      <c r="S176" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA176" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -26153,23 +25527,13 @@
       </c>
       <c r="AP176" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR176" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS176" t="inlineStr"/>
       <c r="AT176" t="n">
         <v>0</v>
       </c>
-      <c r="AU176" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV176" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -26283,14 +25647,12 @@
       <c r="O177" t="n">
         <v>115</v>
       </c>
+      <c r="P177" t="n">
+        <v>115</v>
+      </c>
       <c r="R177" t="n">
         <v>0.03311488952480515</v>
       </c>
-      <c r="S177" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA177" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -26303,23 +25665,13 @@
       </c>
       <c r="AP177" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR177" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS177" t="inlineStr"/>
       <c r="AT177" t="n">
         <v>0</v>
       </c>
-      <c r="AU177" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV177" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -26433,14 +25785,12 @@
       <c r="O178" t="n">
         <v>205</v>
       </c>
+      <c r="P178" t="n">
+        <v>205</v>
+      </c>
       <c r="R178" t="n">
         <v>0.05903089002247875</v>
       </c>
-      <c r="S178" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA178" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -26453,23 +25803,13 @@
       </c>
       <c r="AP178" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR178" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS178" t="inlineStr"/>
       <c r="AT178" t="n">
         <v>0</v>
       </c>
-      <c r="AU178" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV178" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -26583,14 +25923,12 @@
       <c r="O179" t="n">
         <v>134</v>
       </c>
+      <c r="P179" t="n">
+        <v>134</v>
+      </c>
       <c r="R179" t="n">
         <v>0.03858604518542513</v>
       </c>
-      <c r="S179" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA179" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -26603,23 +25941,13 @@
       </c>
       <c r="AP179" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR179" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS179" t="inlineStr"/>
       <c r="AT179" t="n">
         <v>0</v>
       </c>
-      <c r="AU179" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV179" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -27021,14 +26349,12 @@
       <c r="O182" t="n">
         <v>108</v>
       </c>
+      <c r="P182" t="n">
+        <v>108</v>
+      </c>
       <c r="R182" t="n">
         <v>0.03109920059720831</v>
       </c>
-      <c r="S182" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA182" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -27041,23 +26367,13 @@
       </c>
       <c r="AP182" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR182" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS182" t="inlineStr"/>
       <c r="AT182" t="n">
         <v>0</v>
       </c>
-      <c r="AU182" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV182" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -27171,14 +26487,12 @@
       <c r="O183" t="n">
         <v>363</v>
       </c>
+      <c r="P183" t="n">
+        <v>363</v>
+      </c>
       <c r="R183" t="n">
         <v>0.1045278686739502</v>
       </c>
-      <c r="S183" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA183" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -27191,23 +26505,13 @@
       </c>
       <c r="AP183" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR183" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS183" t="inlineStr"/>
       <c r="AT183" t="n">
         <v>0</v>
       </c>
-      <c r="AU183" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV183" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -27321,14 +26625,12 @@
       <c r="O184" t="n">
         <v>140</v>
       </c>
+      <c r="P184" t="n">
+        <v>140</v>
+      </c>
       <c r="R184" t="n">
         <v>0.04031377855193671</v>
       </c>
-      <c r="S184" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA184" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -27341,23 +26643,13 @@
       </c>
       <c r="AP184" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR184" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS184" t="inlineStr"/>
       <c r="AT184" t="n">
         <v>0</v>
       </c>
-      <c r="AU184" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV184" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -27471,14 +26763,12 @@
       <c r="O185" t="n">
         <v>264</v>
       </c>
+      <c r="P185" t="n">
+        <v>264</v>
+      </c>
       <c r="R185" t="n">
         <v>0.07602026812650921</v>
       </c>
-      <c r="S185" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA185" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -27491,23 +26781,13 @@
       </c>
       <c r="AP185" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR185" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS185" t="inlineStr"/>
       <c r="AT185" t="n">
         <v>0</v>
       </c>
-      <c r="AU185" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV185" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -27909,14 +27189,12 @@
       <c r="O188" t="n">
         <v>158</v>
       </c>
+      <c r="P188" t="n">
+        <v>158</v>
+      </c>
       <c r="R188" t="n">
         <v>0.04549697865147143</v>
       </c>
-      <c r="S188" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA188" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -27929,23 +27207,13 @@
       </c>
       <c r="AP188" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR188" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS188" t="inlineStr"/>
       <c r="AT188" t="n">
         <v>0</v>
       </c>
-      <c r="AU188" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV188" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -28059,14 +27327,12 @@
       <c r="O189" t="n">
         <v>334</v>
       </c>
+      <c r="P189" t="n">
+        <v>334</v>
+      </c>
       <c r="R189" t="n">
         <v>0.09617715740247758</v>
       </c>
-      <c r="S189" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA189" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -28079,23 +27345,13 @@
       </c>
       <c r="AP189" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR189" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS189" t="inlineStr"/>
       <c r="AT189" t="n">
         <v>0</v>
       </c>
-      <c r="AU189" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV189" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -28209,14 +27465,12 @@
       <c r="O190" t="n">
         <v>133</v>
       </c>
+      <c r="P190" t="n">
+        <v>133</v>
+      </c>
       <c r="R190" t="n">
         <v>0.03829808962433987</v>
       </c>
-      <c r="S190" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA190" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -28229,23 +27483,13 @@
       </c>
       <c r="AP190" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR190" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS190" t="inlineStr"/>
       <c r="AT190" t="n">
         <v>0</v>
       </c>
-      <c r="AU190" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV190" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -28359,14 +27603,12 @@
       <c r="O191" t="n">
         <v>292</v>
       </c>
+      <c r="P191" t="n">
+        <v>292</v>
+      </c>
       <c r="R191" t="n">
         <v>0.08408302383689656</v>
       </c>
-      <c r="S191" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA191" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -28379,23 +27621,13 @@
       </c>
       <c r="AP191" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR191" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS191" t="inlineStr"/>
       <c r="AT191" t="n">
         <v>0</v>
       </c>
-      <c r="AU191" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV191" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -28509,14 +27741,12 @@
       <c r="O192" t="n">
         <v>110</v>
       </c>
+      <c r="P192" t="n">
+        <v>110</v>
+      </c>
       <c r="R192" t="n">
         <v>0.03167511171937884</v>
       </c>
-      <c r="S192" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA192" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -28529,23 +27759,13 @@
       </c>
       <c r="AP192" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR192" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS192" t="inlineStr"/>
       <c r="AT192" t="n">
         <v>0</v>
       </c>
-      <c r="AU192" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV192" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -28947,14 +28167,12 @@
       <c r="O195" t="n">
         <v>302</v>
       </c>
+      <c r="P195" t="n">
+        <v>302</v>
+      </c>
       <c r="R195" t="n">
         <v>0.08696257944774918</v>
       </c>
-      <c r="S195" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA195" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -28967,23 +28185,13 @@
       </c>
       <c r="AP195" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR195" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS195" t="inlineStr"/>
       <c r="AT195" t="n">
         <v>0</v>
       </c>
-      <c r="AU195" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV195" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -29097,14 +28305,12 @@
       <c r="O196" t="n">
         <v>136</v>
       </c>
+      <c r="P196" t="n">
+        <v>136</v>
+      </c>
       <c r="R196" t="n">
         <v>0.03916195630759566</v>
       </c>
-      <c r="S196" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA196" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -29117,23 +28323,13 @@
       </c>
       <c r="AP196" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR196" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS196" t="inlineStr"/>
       <c r="AT196" t="n">
         <v>0</v>
       </c>
-      <c r="AU196" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV196" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -29247,14 +28443,12 @@
       <c r="O197" t="n">
         <v>295</v>
       </c>
+      <c r="P197" t="n">
+        <v>295</v>
+      </c>
       <c r="R197" t="n">
         <v>0.08494689052015235</v>
       </c>
-      <c r="S197" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA197" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -29267,23 +28461,13 @@
       </c>
       <c r="AP197" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR197" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS197" t="inlineStr"/>
       <c r="AT197" t="n">
         <v>0</v>
       </c>
-      <c r="AU197" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV197" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -29397,14 +28581,12 @@
       <c r="O198" t="n">
         <v>127</v>
       </c>
+      <c r="P198" t="n">
+        <v>127</v>
+      </c>
       <c r="R198" t="n">
         <v>0.03657035625782829</v>
       </c>
-      <c r="S198" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA198" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -29417,23 +28599,13 @@
       </c>
       <c r="AP198" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR198" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS198" t="inlineStr"/>
       <c r="AT198" t="n">
         <v>0</v>
       </c>
-      <c r="AU198" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV198" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -29835,14 +29007,12 @@
       <c r="O201" t="n">
         <v>324</v>
       </c>
+      <c r="P201" t="n">
+        <v>324</v>
+      </c>
       <c r="R201" t="n">
         <v>0.09329760179162494</v>
       </c>
-      <c r="S201" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA201" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -29855,23 +29025,13 @@
       </c>
       <c r="AP201" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR201" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS201" t="inlineStr"/>
       <c r="AT201" t="n">
         <v>0</v>
       </c>
-      <c r="AU201" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV201" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -29985,14 +29145,12 @@
       <c r="O202" t="n">
         <v>141</v>
       </c>
+      <c r="P202" t="n">
+        <v>141</v>
+      </c>
       <c r="R202" t="n">
         <v>0.04060173411302197</v>
       </c>
-      <c r="S202" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA202" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -30005,23 +29163,13 @@
       </c>
       <c r="AP202" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR202" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS202" t="inlineStr"/>
       <c r="AT202" t="n">
         <v>0</v>
       </c>
-      <c r="AU202" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV202" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -30135,14 +29283,12 @@
       <c r="O203" t="n">
         <v>278</v>
       </c>
+      <c r="P203" t="n">
+        <v>278</v>
+      </c>
       <c r="R203" t="n">
         <v>0.08005164598170289</v>
       </c>
-      <c r="S203" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA203" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -30155,23 +29301,13 @@
       </c>
       <c r="AP203" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR203" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS203" t="inlineStr"/>
       <c r="AT203" t="n">
         <v>0</v>
       </c>
-      <c r="AU203" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV203" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -30285,14 +29421,12 @@
       <c r="O204" t="n">
         <v>122</v>
       </c>
+      <c r="P204" t="n">
+        <v>122</v>
+      </c>
       <c r="R204" t="n">
         <v>0.03513057845240199</v>
       </c>
-      <c r="S204" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA204" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -30305,23 +29439,13 @@
       </c>
       <c r="AP204" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR204" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS204" t="inlineStr"/>
       <c r="AT204" t="n">
         <v>0</v>
       </c>
-      <c r="AU204" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV204" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -30435,14 +29559,12 @@
       <c r="O205" t="n">
         <v>95</v>
       </c>
+      <c r="P205" t="n">
+        <v>95</v>
+      </c>
       <c r="R205" t="n">
         <v>0.0273557783030999</v>
       </c>
-      <c r="S205" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA205" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -30455,23 +29577,13 @@
       </c>
       <c r="AP205" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR205" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS205" t="inlineStr"/>
       <c r="AT205" t="n">
         <v>0</v>
       </c>
-      <c r="AU205" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV205" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -30873,14 +29985,12 @@
       <c r="O208" t="n">
         <v>151</v>
       </c>
+      <c r="P208" t="n">
+        <v>151</v>
+      </c>
       <c r="R208" t="n">
         <v>0.04348128972387459</v>
       </c>
-      <c r="S208" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA208" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -30893,23 +30003,13 @@
       </c>
       <c r="AP208" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR208" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS208" t="inlineStr"/>
       <c r="AT208" t="n">
         <v>0</v>
       </c>
-      <c r="AU208" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV208" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -31023,14 +30123,12 @@
       <c r="O209" t="n">
         <v>113</v>
       </c>
+      <c r="P209" t="n">
+        <v>113</v>
+      </c>
       <c r="R209" t="n">
         <v>0.03253897840263462</v>
       </c>
-      <c r="S209" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA209" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -31043,23 +30141,13 @@
       </c>
       <c r="AP209" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR209" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS209" t="inlineStr"/>
       <c r="AT209" t="n">
         <v>0</v>
       </c>
-      <c r="AU209" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV209" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -31173,14 +30261,12 @@
       <c r="O210" t="n">
         <v>463</v>
       </c>
+      <c r="P210" t="n">
+        <v>463</v>
+      </c>
       <c r="R210" t="n">
         <v>0.1333234247824764</v>
       </c>
-      <c r="S210" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA210" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -31193,23 +30279,13 @@
       </c>
       <c r="AP210" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR210" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS210" t="inlineStr"/>
       <c r="AT210" t="n">
         <v>0</v>
       </c>
-      <c r="AU210" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV210" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -31323,14 +30399,12 @@
       <c r="O211" t="n">
         <v>99</v>
       </c>
+      <c r="P211" t="n">
+        <v>99</v>
+      </c>
       <c r="R211" t="n">
         <v>0.02850760054744096</v>
       </c>
-      <c r="S211" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA211" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -31343,23 +30417,13 @@
       </c>
       <c r="AP211" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR211" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS211" t="inlineStr"/>
       <c r="AT211" t="n">
         <v>0</v>
       </c>
-      <c r="AU211" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV211" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -31761,14 +30825,12 @@
       <c r="O214" t="n">
         <v>74</v>
       </c>
+      <c r="P214" t="n">
+        <v>74</v>
+      </c>
       <c r="R214" t="n">
         <v>0.0213087115203094</v>
       </c>
-      <c r="S214" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA214" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -31781,23 +30843,13 @@
       </c>
       <c r="AP214" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR214" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS214" t="inlineStr"/>
       <c r="AT214" t="n">
         <v>0</v>
       </c>
-      <c r="AU214" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV214" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -31911,14 +30963,12 @@
       <c r="O215" t="n">
         <v>145</v>
       </c>
+      <c r="P215" t="n">
+        <v>145</v>
+      </c>
       <c r="R215" t="n">
         <v>0.04175355635736302</v>
       </c>
-      <c r="S215" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA215" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -31931,23 +30981,13 @@
       </c>
       <c r="AP215" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR215" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS215" t="inlineStr"/>
       <c r="AT215" t="n">
         <v>0</v>
       </c>
-      <c r="AU215" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV215" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -32061,14 +31101,12 @@
       <c r="O216" t="n">
         <v>117</v>
       </c>
+      <c r="P216" t="n">
+        <v>117</v>
+      </c>
       <c r="R216" t="n">
         <v>0.03369080064697567</v>
       </c>
-      <c r="S216" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA216" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -32081,23 +31119,13 @@
       </c>
       <c r="AP216" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR216" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS216" t="inlineStr"/>
       <c r="AT216" t="n">
         <v>0</v>
       </c>
-      <c r="AU216" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV216" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -32211,14 +31239,12 @@
       <c r="O217" t="n">
         <v>112</v>
       </c>
+      <c r="P217" t="n">
+        <v>112</v>
+      </c>
       <c r="R217" t="n">
         <v>0.03225102284154936</v>
       </c>
-      <c r="S217" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA217" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -32231,23 +31257,13 @@
       </c>
       <c r="AP217" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR217" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS217" t="inlineStr"/>
       <c r="AT217" t="n">
         <v>0</v>
       </c>
-      <c r="AU217" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV217" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -32649,14 +31665,12 @@
       <c r="O220" t="n">
         <v>294</v>
       </c>
+      <c r="P220" t="n">
+        <v>294</v>
+      </c>
       <c r="R220" t="n">
         <v>0.08465893495906708</v>
       </c>
-      <c r="S220" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA220" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -32669,23 +31683,13 @@
       </c>
       <c r="AP220" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR220" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS220" t="inlineStr"/>
       <c r="AT220" t="n">
         <v>0</v>
       </c>
-      <c r="AU220" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV220" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -32799,14 +31803,12 @@
       <c r="O221" t="n">
         <v>100</v>
       </c>
+      <c r="P221" t="n">
+        <v>100</v>
+      </c>
       <c r="R221" t="n">
         <v>0.02879555610852622</v>
       </c>
-      <c r="S221" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA221" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -32819,23 +31821,13 @@
       </c>
       <c r="AP221" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR221" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS221" t="inlineStr"/>
       <c r="AT221" t="n">
         <v>0</v>
       </c>
-      <c r="AU221" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV221" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -32949,14 +31941,12 @@
       <c r="O222" t="n">
         <v>272</v>
       </c>
+      <c r="P222" t="n">
+        <v>272</v>
+      </c>
       <c r="R222" t="n">
         <v>0.07832391261519131</v>
       </c>
-      <c r="S222" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA222" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -32969,23 +31959,13 @@
       </c>
       <c r="AP222" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR222" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS222" t="inlineStr"/>
       <c r="AT222" t="n">
         <v>0</v>
       </c>
-      <c r="AU222" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV222" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -33099,14 +32079,12 @@
       <c r="O223" t="n">
         <v>297</v>
       </c>
+      <c r="P223" t="n">
+        <v>297</v>
+      </c>
       <c r="R223" t="n">
         <v>0.08552280164232287</v>
       </c>
-      <c r="S223" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA223" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -33119,23 +32097,13 @@
       </c>
       <c r="AP223" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR223" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS223" t="inlineStr"/>
       <c r="AT223" t="n">
         <v>0</v>
       </c>
-      <c r="AU223" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV223" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -33249,14 +32217,12 @@
       <c r="O224" t="n">
         <v>153</v>
       </c>
+      <c r="P224" t="n">
+        <v>153</v>
+      </c>
       <c r="R224" t="n">
         <v>0.04405720084604511</v>
       </c>
-      <c r="S224" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA224" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -33269,23 +32235,13 @@
       </c>
       <c r="AP224" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR224" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS224" t="inlineStr"/>
       <c r="AT224" t="n">
         <v>0</v>
       </c>
-      <c r="AU224" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV224" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -33687,14 +32643,12 @@
       <c r="O227" t="n">
         <v>314</v>
       </c>
+      <c r="P227" t="n">
+        <v>314</v>
+      </c>
       <c r="R227" t="n">
         <v>0.09041804618077232</v>
       </c>
-      <c r="S227" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA227" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -33707,23 +32661,13 @@
       </c>
       <c r="AP227" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR227" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS227" t="inlineStr"/>
       <c r="AT227" t="n">
         <v>0</v>
       </c>
-      <c r="AU227" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV227" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -33837,14 +32781,12 @@
       <c r="O228" t="n">
         <v>101</v>
       </c>
+      <c r="P228" t="n">
+        <v>101</v>
+      </c>
       <c r="R228" t="n">
         <v>0.02908351166961148</v>
       </c>
-      <c r="S228" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA228" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -33857,23 +32799,13 @@
       </c>
       <c r="AP228" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR228" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS228" t="inlineStr"/>
       <c r="AT228" t="n">
         <v>0</v>
       </c>
-      <c r="AU228" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV228" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -33987,14 +32919,12 @@
       <c r="O229" t="n">
         <v>190</v>
       </c>
+      <c r="P229" t="n">
+        <v>190</v>
+      </c>
       <c r="R229" t="n">
         <v>0.05471155660619981</v>
       </c>
-      <c r="S229" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA229" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -34007,23 +32937,13 @@
       </c>
       <c r="AP229" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR229" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS229" t="inlineStr"/>
       <c r="AT229" t="n">
         <v>0</v>
       </c>
-      <c r="AU229" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV229" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -34137,14 +33057,12 @@
       <c r="O230" t="n">
         <v>100</v>
       </c>
+      <c r="P230" t="n">
+        <v>100</v>
+      </c>
       <c r="R230" t="n">
         <v>0.02879555610852622</v>
       </c>
-      <c r="S230" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA230" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -34157,23 +33075,13 @@
       </c>
       <c r="AP230" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR230" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS230" t="inlineStr"/>
       <c r="AT230" t="n">
         <v>0</v>
       </c>
-      <c r="AU230" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV230" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -34575,14 +33483,12 @@
       <c r="O233" t="n">
         <v>304</v>
       </c>
+      <c r="P233" t="n">
+        <v>304</v>
+      </c>
       <c r="R233" t="n">
         <v>0.08753849056991971</v>
       </c>
-      <c r="S233" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA233" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -34595,23 +33501,13 @@
       </c>
       <c r="AP233" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR233" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS233" t="inlineStr"/>
       <c r="AT233" t="n">
         <v>0</v>
       </c>
-      <c r="AU233" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV233" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -34725,14 +33621,12 @@
       <c r="O234" t="n">
         <v>124</v>
       </c>
+      <c r="P234" t="n">
+        <v>124</v>
+      </c>
       <c r="R234" t="n">
         <v>0.03570648957457252</v>
       </c>
-      <c r="S234" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA234" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -34745,23 +33639,13 @@
       </c>
       <c r="AP234" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR234" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS234" t="inlineStr"/>
       <c r="AT234" t="n">
         <v>0</v>
       </c>
-      <c r="AU234" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV234" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -34875,14 +33759,12 @@
       <c r="O235" t="n">
         <v>244</v>
       </c>
+      <c r="P235" t="n">
+        <v>244</v>
+      </c>
       <c r="R235" t="n">
         <v>0.07026115690480397</v>
       </c>
-      <c r="S235" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA235" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -34895,23 +33777,13 @@
       </c>
       <c r="AP235" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR235" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS235" t="inlineStr"/>
       <c r="AT235" t="n">
         <v>0</v>
       </c>
-      <c r="AU235" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV235" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -35025,14 +33897,12 @@
       <c r="O236" t="n">
         <v>111</v>
       </c>
+      <c r="P236" t="n">
+        <v>111</v>
+      </c>
       <c r="R236" t="n">
         <v>0.0319630672804641</v>
       </c>
-      <c r="S236" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA236" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -35045,23 +33915,13 @@
       </c>
       <c r="AP236" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR236" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS236" t="inlineStr"/>
       <c r="AT236" t="n">
         <v>0</v>
       </c>
-      <c r="AU236" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV236" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -35463,14 +34323,12 @@
       <c r="O239" t="n">
         <v>135</v>
       </c>
+      <c r="P239" t="n">
+        <v>135</v>
+      </c>
       <c r="R239" t="n">
         <v>0.03887400074651039</v>
       </c>
-      <c r="S239" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA239" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -35483,23 +34341,13 @@
       </c>
       <c r="AP239" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR239" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS239" t="inlineStr"/>
       <c r="AT239" t="n">
         <v>0</v>
       </c>
-      <c r="AU239" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV239" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -35613,14 +34461,12 @@
       <c r="O240" t="n">
         <v>285</v>
       </c>
+      <c r="P240" t="n">
+        <v>285</v>
+      </c>
       <c r="R240" t="n">
         <v>0.08206733490929972</v>
       </c>
-      <c r="S240" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA240" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -35633,23 +34479,13 @@
       </c>
       <c r="AP240" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR240" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS240" t="inlineStr"/>
       <c r="AT240" t="n">
         <v>0</v>
       </c>
-      <c r="AU240" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV240" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -35763,14 +34599,12 @@
       <c r="O241" t="n">
         <v>110</v>
       </c>
+      <c r="P241" t="n">
+        <v>110</v>
+      </c>
       <c r="R241" t="n">
         <v>0.03167511171937884</v>
       </c>
-      <c r="S241" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA241" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -35783,23 +34617,13 @@
       </c>
       <c r="AP241" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR241" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS241" t="inlineStr"/>
       <c r="AT241" t="n">
         <v>0</v>
       </c>
-      <c r="AU241" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV241" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -35913,14 +34737,12 @@
       <c r="O242" t="n">
         <v>276</v>
       </c>
+      <c r="P242" t="n">
+        <v>276</v>
+      </c>
       <c r="R242" t="n">
         <v>0.07947573485953237</v>
       </c>
-      <c r="S242" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA242" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -35933,23 +34755,13 @@
       </c>
       <c r="AP242" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR242" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS242" t="inlineStr"/>
       <c r="AT242" t="n">
         <v>0</v>
       </c>
-      <c r="AU242" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV242" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -36063,14 +34875,12 @@
       <c r="O243" t="n">
         <v>117</v>
       </c>
+      <c r="P243" t="n">
+        <v>117</v>
+      </c>
       <c r="R243" t="n">
         <v>0.03369080064697567</v>
       </c>
-      <c r="S243" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA243" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -36083,23 +34893,13 @@
       </c>
       <c r="AP243" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR243" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS243" t="inlineStr"/>
       <c r="AT243" t="n">
         <v>0</v>
       </c>
-      <c r="AU243" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV243" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -36501,14 +35301,12 @@
       <c r="O246" t="n">
         <v>136</v>
       </c>
+      <c r="P246" t="n">
+        <v>136</v>
+      </c>
       <c r="R246" t="n">
         <v>0.03916195630759566</v>
       </c>
-      <c r="S246" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA246" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -36521,23 +35319,13 @@
       </c>
       <c r="AP246" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR246" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS246" t="inlineStr"/>
       <c r="AT246" t="n">
         <v>0</v>
       </c>
-      <c r="AU246" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV246" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -36651,14 +35439,12 @@
       <c r="O247" t="n">
         <v>110</v>
       </c>
+      <c r="P247" t="n">
+        <v>110</v>
+      </c>
       <c r="R247" t="n">
         <v>0.03167511171937884</v>
       </c>
-      <c r="S247" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA247" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -36671,23 +35457,13 @@
       </c>
       <c r="AP247" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR247" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS247" t="inlineStr"/>
       <c r="AT247" t="n">
         <v>0</v>
       </c>
-      <c r="AU247" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV247" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -36801,14 +35577,12 @@
       <c r="O248" t="n">
         <v>338</v>
       </c>
+      <c r="P248" t="n">
+        <v>338</v>
+      </c>
       <c r="R248" t="n">
         <v>0.09732897964681861</v>
       </c>
-      <c r="S248" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA248" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -36821,23 +35595,13 @@
       </c>
       <c r="AP248" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR248" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS248" t="inlineStr"/>
       <c r="AT248" t="n">
         <v>0</v>
       </c>
-      <c r="AU248" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV248" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -36951,14 +35715,12 @@
       <c r="O249" t="n">
         <v>83</v>
       </c>
+      <c r="P249" t="n">
+        <v>83</v>
+      </c>
       <c r="R249" t="n">
         <v>0.02390031157007676</v>
       </c>
-      <c r="S249" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA249" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -36971,22 +35733,12 @@
       </c>
       <c r="AP249" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR249" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS249" t="inlineStr"/>
       <c r="AT249" t="n">
         <v>0</v>
-      </c>
-      <c r="AU249" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV249" t="inlineStr">
         <is>
